--- a/artfynd/A 60139-2024 artfynd.xlsx
+++ b/artfynd/A 60139-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67353663</v>
+        <v>5029537</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -723,17 +718,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Osaboda, Sm</t>
+          <t>Osaboda, Ryssby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451461.9933338456</v>
+        <v>451444</v>
       </c>
       <c r="R2" t="n">
-        <v>6299850.642055972</v>
+        <v>6299824</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,27 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-12-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I en bukett. Friska träd.</t>
+          <t>2006-12-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,6 +771,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövskogsdunge</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -804,6 +788,359 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115843384</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Osaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>451432</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6299825</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lövskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>67353663</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Osaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>451462</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6299851</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I en bukett. Friska träd.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>67353684</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Osaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>451447</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6299821</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ryssby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I en bukett. Friska träd.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60139-2024 artfynd.xlsx
+++ b/artfynd/A 60139-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5029537</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115843384</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67353663</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,8 +1161,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67353684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>